--- a/Behind/june 2026/STT Report JUNE 2026.xlsx
+++ b/Behind/june 2026/STT Report JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546F29D5-8F12-4B44-B0E5-B4758FCB0D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC56300-72C5-4E0A-8DC9-9F80A3C5036D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2629,22 +2629,22 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,11 +2656,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3041,44 +3041,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="115" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="115" t="s">
+      <c r="A1" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="116" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="116" t="s">
+      <c r="C1" s="111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="116" t="s">
+      <c r="E1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="116" t="s">
+      <c r="F1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115" t="s">
+      <c r="G1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="116" t="s">
+      <c r="H1" s="111" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="115" t="s">
+      <c r="K1" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="120" t="s">
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
       <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
@@ -3094,61 +3094,61 @@
       <c r="Y1" s="119"/>
       <c r="Z1" s="119"/>
       <c r="AA1" s="119"/>
-      <c r="AB1" s="113" t="s">
+      <c r="AB1" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="113" t="s">
+      <c r="AC1" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="113" t="s">
+      <c r="AD1" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="113" t="s">
+      <c r="AE1" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="113" t="s">
+      <c r="AF1" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="113" t="s">
+      <c r="AG1" s="115" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="113" t="s">
+      <c r="AI1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="113" t="s">
+      <c r="AJ1" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="113" t="s">
+      <c r="AK1" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="113" t="s">
+      <c r="AL1" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="113" t="s">
+      <c r="AM1" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="111" t="s">
+      <c r="AN1" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="111" t="s">
+      <c r="AO1" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="113" t="s">
+      <c r="AP1" s="115" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="115"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="116"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="111"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3204,23 +3204,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="114"/>
-      <c r="AG2" s="114"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
+      <c r="AE2" s="116"/>
+      <c r="AF2" s="116"/>
+      <c r="AG2" s="116"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="114"/>
-      <c r="AJ2" s="114"/>
-      <c r="AK2" s="114"/>
-      <c r="AL2" s="114"/>
-      <c r="AM2" s="114"/>
-      <c r="AN2" s="112"/>
-      <c r="AO2" s="112"/>
-      <c r="AP2" s="114"/>
+      <c r="AI2" s="116"/>
+      <c r="AJ2" s="116"/>
+      <c r="AK2" s="116"/>
+      <c r="AL2" s="116"/>
+      <c r="AM2" s="116"/>
+      <c r="AN2" s="121"/>
+      <c r="AO2" s="121"/>
+      <c r="AP2" s="116"/>
     </row>
     <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="70">
@@ -58222,13 +58222,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58241,14 +58242,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Behind/june 2026/STT Report JUNE 2026.xlsx
+++ b/Behind/june 2026/STT Report JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC56300-72C5-4E0A-8DC9-9F80A3C5036D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF73D9A0-2AB1-4BC0-9DDB-6A0860308E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2629,22 +2629,22 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,11 +2656,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2998,7 +2998,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP431"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3041,44 +3040,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="114" t="s">
+      <c r="A1" s="115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="111" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="111" t="s">
+      <c r="C1" s="116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="111" t="s">
+      <c r="E1" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="111" t="s">
+      <c r="F1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="114" t="s">
+      <c r="G1" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="111" t="s">
+      <c r="H1" s="116" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="114" t="s">
+      <c r="K1" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="112" t="s">
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
       <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
@@ -3094,61 +3093,61 @@
       <c r="Y1" s="119"/>
       <c r="Z1" s="119"/>
       <c r="AA1" s="119"/>
-      <c r="AB1" s="115" t="s">
+      <c r="AB1" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="115" t="s">
+      <c r="AC1" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="115" t="s">
+      <c r="AD1" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="115" t="s">
+      <c r="AE1" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="115" t="s">
+      <c r="AF1" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="115" t="s">
+      <c r="AG1" s="113" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="115" t="s">
+      <c r="AI1" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="115" t="s">
+      <c r="AJ1" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="115" t="s">
+      <c r="AK1" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="115" t="s">
+      <c r="AL1" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="115" t="s">
+      <c r="AM1" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="120" t="s">
+      <c r="AN1" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="120" t="s">
+      <c r="AO1" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="115" t="s">
+      <c r="AP1" s="113" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="111"/>
+    <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="115"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="116"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3204,25 +3203,25 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="116"/>
-      <c r="AG2" s="116"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
+      <c r="AE2" s="114"/>
+      <c r="AF2" s="114"/>
+      <c r="AG2" s="114"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="116"/>
-      <c r="AJ2" s="116"/>
-      <c r="AK2" s="116"/>
-      <c r="AL2" s="116"/>
-      <c r="AM2" s="116"/>
-      <c r="AN2" s="121"/>
-      <c r="AO2" s="121"/>
-      <c r="AP2" s="116"/>
+      <c r="AI2" s="114"/>
+      <c r="AJ2" s="114"/>
+      <c r="AK2" s="114"/>
+      <c r="AL2" s="114"/>
+      <c r="AM2" s="114"/>
+      <c r="AN2" s="112"/>
+      <c r="AO2" s="112"/>
+      <c r="AP2" s="114"/>
     </row>
-    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="70">
         <v>46174</v>
       </c>
@@ -3359,7 +3358,7 @@
       <c r="AO3" s="6"/>
       <c r="AP3" s="12"/>
     </row>
-    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" s="70">
         <v>46174</v>
       </c>
@@ -3496,7 +3495,7 @@
       <c r="AO4" s="6"/>
       <c r="AP4" s="12"/>
     </row>
-    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="70">
         <v>46174</v>
       </c>
@@ -3633,7 +3632,7 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="12"/>
     </row>
-    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6" s="70">
         <v>46174</v>
       </c>
@@ -3770,7 +3769,7 @@
       <c r="AO6" s="6"/>
       <c r="AP6" s="12"/>
     </row>
-    <row r="7" spans="1:42" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="70">
         <v>46175</v>
       </c>
@@ -3916,7 +3915,7 @@
       </c>
       <c r="AP7" s="12"/>
     </row>
-    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8" s="70">
         <v>46175</v>
       </c>
@@ -4051,7 +4050,7 @@
       <c r="AN8"/>
       <c r="AP8" s="12"/>
     </row>
-    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9" s="70">
         <v>46175</v>
       </c>
@@ -4186,7 +4185,7 @@
       <c r="AN9"/>
       <c r="AP9" s="12"/>
     </row>
-    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A10" s="70">
         <v>46175</v>
       </c>
@@ -4320,7 +4319,7 @@
       </c>
       <c r="AP10" s="12"/>
     </row>
-    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11" s="70">
         <v>46175</v>
       </c>
@@ -4454,7 +4453,7 @@
       </c>
       <c r="AP11" s="12"/>
     </row>
-    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12" s="70">
         <v>46175</v>
       </c>
@@ -4588,7 +4587,7 @@
       </c>
       <c r="AP12" s="12"/>
     </row>
-    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13" s="70">
         <v>46176</v>
       </c>
@@ -4722,7 +4721,7 @@
       </c>
       <c r="AP13" s="12"/>
     </row>
-    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14" s="70">
         <v>46176</v>
       </c>
@@ -4856,7 +4855,7 @@
       </c>
       <c r="AP14" s="12"/>
     </row>
-    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15" s="70">
         <v>46176</v>
       </c>
@@ -4990,7 +4989,7 @@
       </c>
       <c r="AP15" s="12"/>
     </row>
-    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16" s="70">
         <v>46176</v>
       </c>
@@ -5124,7 +5123,7 @@
       </c>
       <c r="AP16" s="12"/>
     </row>
-    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A17" s="70">
         <v>46176</v>
       </c>
@@ -5258,7 +5257,7 @@
       </c>
       <c r="AP17" s="12"/>
     </row>
-    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" s="70">
         <v>46176</v>
       </c>
@@ -5392,7 +5391,7 @@
       </c>
       <c r="AP18" s="12"/>
     </row>
-    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A19" s="70">
         <v>46176</v>
       </c>
@@ -5526,7 +5525,7 @@
       </c>
       <c r="AP19" s="12"/>
     </row>
-    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" s="70">
         <v>46176</v>
       </c>
@@ -5660,7 +5659,7 @@
       </c>
       <c r="AP20" s="12"/>
     </row>
-    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" s="70">
         <v>46176</v>
       </c>
@@ -5794,7 +5793,7 @@
       </c>
       <c r="AP21" s="12"/>
     </row>
-    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" s="70">
         <v>46176</v>
       </c>
@@ -5928,7 +5927,7 @@
       </c>
       <c r="AP22" s="12"/>
     </row>
-    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" s="70">
         <v>46176</v>
       </c>
@@ -6062,7 +6061,7 @@
       </c>
       <c r="AP23" s="12"/>
     </row>
-    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" s="70">
         <v>46177</v>
       </c>
@@ -6196,7 +6195,7 @@
       </c>
       <c r="AP24" s="12"/>
     </row>
-    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" s="70">
         <v>46177</v>
       </c>
@@ -6330,7 +6329,7 @@
       </c>
       <c r="AP25" s="12"/>
     </row>
-    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" s="70">
         <v>46177</v>
       </c>
@@ -6464,7 +6463,7 @@
       </c>
       <c r="AP26" s="12"/>
     </row>
-    <row r="27" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27" s="70">
         <v>46177</v>
       </c>
@@ -6598,7 +6597,7 @@
       </c>
       <c r="AP27" s="12"/>
     </row>
-    <row r="28" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A28" s="70">
         <v>46177</v>
       </c>
@@ -6732,7 +6731,7 @@
       </c>
       <c r="AP28" s="12"/>
     </row>
-    <row r="29" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A29" s="70">
         <v>46178</v>
       </c>
@@ -6866,7 +6865,7 @@
       </c>
       <c r="AP29" s="12"/>
     </row>
-    <row r="30" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A30" s="70">
         <v>46178</v>
       </c>
@@ -7000,7 +6999,7 @@
       </c>
       <c r="AP30" s="12"/>
     </row>
-    <row r="31" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A31" s="70">
         <v>46178</v>
       </c>
@@ -7134,7 +7133,7 @@
       </c>
       <c r="AP31" s="12"/>
     </row>
-    <row r="32" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A32" s="70">
         <v>46178</v>
       </c>
@@ -7268,7 +7267,7 @@
       </c>
       <c r="AP32" s="12"/>
     </row>
-    <row r="33" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" s="70">
         <v>46178</v>
       </c>
@@ -7402,7 +7401,7 @@
       </c>
       <c r="AP33" s="12"/>
     </row>
-    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" s="70">
         <v>46178</v>
       </c>
@@ -7536,7 +7535,7 @@
       </c>
       <c r="AP34" s="12"/>
     </row>
-    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" s="70">
         <v>46209</v>
       </c>
@@ -7670,7 +7669,7 @@
       </c>
       <c r="AP35" s="12"/>
     </row>
-    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" s="70">
         <v>46209</v>
       </c>
@@ -7804,7 +7803,7 @@
       </c>
       <c r="AP36" s="12"/>
     </row>
-    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" s="70">
         <v>46209</v>
       </c>
@@ -7938,7 +7937,7 @@
       </c>
       <c r="AP37" s="12"/>
     </row>
-    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" s="70">
         <v>46209</v>
       </c>
@@ -8474,7 +8473,7 @@
       </c>
       <c r="AP41" s="12"/>
     </row>
-    <row r="42" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A42" s="70">
         <v>46211</v>
       </c>
@@ -8606,7 +8605,7 @@
       </c>
       <c r="AP42" s="12"/>
     </row>
-    <row r="43" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A43" s="70">
         <v>46211</v>
       </c>
@@ -8738,7 +8737,7 @@
       </c>
       <c r="AP43" s="12"/>
     </row>
-    <row r="44" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A44" s="70">
         <v>46211</v>
       </c>
@@ -9134,7 +9133,7 @@
       </c>
       <c r="AP46" s="12"/>
     </row>
-    <row r="47" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A47" s="70">
         <v>46211</v>
       </c>
@@ -9264,7 +9263,7 @@
       </c>
       <c r="AP47" s="12"/>
     </row>
-    <row r="48" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A48" s="70">
         <v>46211</v>
       </c>
@@ -9396,7 +9395,7 @@
       </c>
       <c r="AP48" s="12"/>
     </row>
-    <row r="49" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A49" s="70">
         <v>46211</v>
       </c>
@@ -9524,7 +9523,7 @@
       </c>
       <c r="AP49" s="12"/>
     </row>
-    <row r="50" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A50" s="70">
         <v>46211</v>
       </c>
@@ -9656,7 +9655,7 @@
       </c>
       <c r="AP50" s="12"/>
     </row>
-    <row r="51" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A51" s="70">
         <v>46211</v>
       </c>
@@ -9786,7 +9785,7 @@
       </c>
       <c r="AP51" s="12"/>
     </row>
-    <row r="52" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A52" s="70">
         <v>46212</v>
       </c>
@@ -9920,7 +9919,7 @@
       </c>
       <c r="AP52" s="12"/>
     </row>
-    <row r="53" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A53" s="70">
         <v>46212</v>
       </c>
@@ -10050,7 +10049,7 @@
       </c>
       <c r="AP53" s="12"/>
     </row>
-    <row r="54" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" s="70">
         <v>46212</v>
       </c>
@@ -10184,7 +10183,7 @@
       </c>
       <c r="AP54" s="12"/>
     </row>
-    <row r="55" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A55" s="70">
         <v>46212</v>
       </c>
@@ -10318,7 +10317,7 @@
       </c>
       <c r="AP55" s="12"/>
     </row>
-    <row r="56" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A56" s="70">
         <v>46212</v>
       </c>
@@ -10452,7 +10451,7 @@
       </c>
       <c r="AP56" s="12"/>
     </row>
-    <row r="57" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A57" s="70">
         <v>46212</v>
       </c>
@@ -10586,7 +10585,7 @@
       </c>
       <c r="AP57" s="12"/>
     </row>
-    <row r="58" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A58" s="70">
         <v>46212</v>
       </c>
@@ -10720,7 +10719,7 @@
       </c>
       <c r="AP58" s="12"/>
     </row>
-    <row r="59" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A59" s="70">
         <v>46212</v>
       </c>
@@ -10854,7 +10853,7 @@
       </c>
       <c r="AP59" s="12"/>
     </row>
-    <row r="60" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A60" s="70">
         <v>46212</v>
       </c>
@@ -11252,7 +11251,7 @@
       </c>
       <c r="AP62" s="12"/>
     </row>
-    <row r="63" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A63" s="70">
         <v>46212</v>
       </c>
@@ -11386,7 +11385,7 @@
       </c>
       <c r="AP63" s="12"/>
     </row>
-    <row r="64" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A64" s="70">
         <v>46212</v>
       </c>
@@ -11520,7 +11519,7 @@
       </c>
       <c r="AP64" s="12"/>
     </row>
-    <row r="65" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A65" s="70">
         <v>46212</v>
       </c>
@@ -11654,7 +11653,7 @@
       </c>
       <c r="AP65" s="12"/>
     </row>
-    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" s="70">
         <v>46212</v>
       </c>
@@ -11788,7 +11787,7 @@
       </c>
       <c r="AP66" s="12"/>
     </row>
-    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" s="70">
         <v>46212</v>
       </c>
@@ -11922,7 +11921,7 @@
       </c>
       <c r="AP67" s="12"/>
     </row>
-    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" s="70">
         <v>46212</v>
       </c>
@@ -12056,7 +12055,7 @@
       </c>
       <c r="AP68" s="12"/>
     </row>
-    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" s="70">
         <v>46212</v>
       </c>
@@ -12190,7 +12189,7 @@
       </c>
       <c r="AP69" s="12"/>
     </row>
-    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" s="70">
         <v>46212</v>
       </c>
@@ -12324,7 +12323,7 @@
       </c>
       <c r="AP70" s="12"/>
     </row>
-    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" s="70">
         <v>46212</v>
       </c>
@@ -12458,7 +12457,7 @@
       </c>
       <c r="AP71" s="12"/>
     </row>
-    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" s="70">
         <v>46183</v>
       </c>
@@ -12592,7 +12591,7 @@
       </c>
       <c r="AP72" s="12"/>
     </row>
-    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" s="70">
         <v>46183</v>
       </c>
@@ -12726,7 +12725,7 @@
       </c>
       <c r="AP73" s="12"/>
     </row>
-    <row r="74" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A74" s="70">
         <v>46183</v>
       </c>
@@ -12860,7 +12859,7 @@
       </c>
       <c r="AP74" s="12"/>
     </row>
-    <row r="75" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A75" s="70">
         <v>46183</v>
       </c>
@@ -12994,7 +12993,7 @@
       </c>
       <c r="AP75" s="12"/>
     </row>
-    <row r="76" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A76" s="70">
         <v>46183</v>
       </c>
@@ -13524,7 +13523,7 @@
       </c>
       <c r="AP79" s="12"/>
     </row>
-    <row r="80" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A80" s="70">
         <v>46184</v>
       </c>
@@ -13658,7 +13657,7 @@
       </c>
       <c r="AP80" s="12"/>
     </row>
-    <row r="81" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A81" s="70">
         <v>46184</v>
       </c>
@@ -13792,7 +13791,7 @@
       </c>
       <c r="AP81" s="12"/>
     </row>
-    <row r="82" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A82" s="70">
         <v>46184</v>
       </c>
@@ -13926,7 +13925,7 @@
       </c>
       <c r="AP82" s="12"/>
     </row>
-    <row r="83" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A83" s="70">
         <v>46184</v>
       </c>
@@ -14060,7 +14059,7 @@
       </c>
       <c r="AP83" s="12"/>
     </row>
-    <row r="84" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A84" s="70">
         <v>46184</v>
       </c>
@@ -14194,7 +14193,7 @@
       </c>
       <c r="AP84" s="12"/>
     </row>
-    <row r="85" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A85" s="70">
         <v>46184</v>
       </c>
@@ -14328,7 +14327,7 @@
       </c>
       <c r="AP85" s="12"/>
     </row>
-    <row r="86" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A86" s="70">
         <v>46184</v>
       </c>
@@ -14462,7 +14461,7 @@
       </c>
       <c r="AP86" s="12"/>
     </row>
-    <row r="87" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A87" s="70">
         <v>46184</v>
       </c>
@@ -14596,7 +14595,7 @@
       </c>
       <c r="AP87" s="12"/>
     </row>
-    <row r="88" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A88" s="70">
         <v>46184</v>
       </c>
@@ -14730,7 +14729,7 @@
       </c>
       <c r="AP88" s="12"/>
     </row>
-    <row r="89" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A89" s="70">
         <v>46184</v>
       </c>
@@ -14864,7 +14863,7 @@
       </c>
       <c r="AP89" s="12"/>
     </row>
-    <row r="90" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A90" s="70">
         <v>46184</v>
       </c>
@@ -14998,7 +14997,7 @@
       </c>
       <c r="AP90" s="12"/>
     </row>
-    <row r="91" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A91" s="70">
         <v>46184</v>
       </c>
@@ -15658,7 +15657,7 @@
       </c>
       <c r="AP95" s="12"/>
     </row>
-    <row r="96" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A96" s="70">
         <v>46185</v>
       </c>
@@ -15792,7 +15791,7 @@
       </c>
       <c r="AP96" s="12"/>
     </row>
-    <row r="97" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A97" s="70">
         <v>46185</v>
       </c>
@@ -15926,7 +15925,7 @@
       </c>
       <c r="AP97" s="12"/>
     </row>
-    <row r="98" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A98" s="70">
         <v>46185</v>
       </c>
@@ -16060,7 +16059,7 @@
       </c>
       <c r="AP98" s="12"/>
     </row>
-    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A99" s="70">
         <v>46185</v>
       </c>
@@ -16194,7 +16193,7 @@
       </c>
       <c r="AP99" s="12"/>
     </row>
-    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A100" s="70">
         <v>46185</v>
       </c>
@@ -16328,7 +16327,7 @@
       </c>
       <c r="AP100" s="12"/>
     </row>
-    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A101" s="70">
         <v>46185</v>
       </c>
@@ -16462,7 +16461,7 @@
       </c>
       <c r="AP101" s="12"/>
     </row>
-    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A102" s="70">
         <v>46185</v>
       </c>
@@ -16596,7 +16595,7 @@
       </c>
       <c r="AP102" s="12"/>
     </row>
-    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A103" s="70">
         <v>46185</v>
       </c>
@@ -16730,7 +16729,7 @@
       </c>
       <c r="AP103" s="12"/>
     </row>
-    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A104" s="70">
         <v>46185</v>
       </c>
@@ -16864,7 +16863,7 @@
       </c>
       <c r="AP104" s="12"/>
     </row>
-    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A105" s="70">
         <v>46185</v>
       </c>
@@ -17130,7 +17129,7 @@
       </c>
       <c r="AP106" s="12"/>
     </row>
-    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A107" s="70">
         <v>46186</v>
       </c>
@@ -17264,7 +17263,7 @@
       </c>
       <c r="AP107" s="12"/>
     </row>
-    <row r="108" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A108" s="70">
         <v>46186</v>
       </c>
@@ -17398,7 +17397,7 @@
       </c>
       <c r="AP108" s="12"/>
     </row>
-    <row r="109" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A109" s="70">
         <v>46186</v>
       </c>
@@ -17532,7 +17531,7 @@
       </c>
       <c r="AP109" s="12"/>
     </row>
-    <row r="110" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A110" s="70">
         <v>46186</v>
       </c>
@@ -17666,7 +17665,7 @@
       </c>
       <c r="AP110" s="12"/>
     </row>
-    <row r="111" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A111" s="70">
         <v>46186</v>
       </c>
@@ -17800,7 +17799,7 @@
       </c>
       <c r="AP111" s="12"/>
     </row>
-    <row r="112" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A112" s="70">
         <v>46186</v>
       </c>
@@ -17934,7 +17933,7 @@
       </c>
       <c r="AP112" s="12"/>
     </row>
-    <row r="113" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A113" s="70">
         <v>46186</v>
       </c>
@@ -18068,7 +18067,7 @@
       </c>
       <c r="AP113" s="12"/>
     </row>
-    <row r="114" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A114" s="70">
         <v>46186</v>
       </c>
@@ -19006,7 +19005,7 @@
       </c>
       <c r="AP120" s="12"/>
     </row>
-    <row r="121" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A121" s="70">
         <v>46188</v>
       </c>
@@ -19140,7 +19139,7 @@
       </c>
       <c r="AP121" s="12"/>
     </row>
-    <row r="122" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A122" s="70">
         <v>46188</v>
       </c>
@@ -19274,7 +19273,7 @@
       </c>
       <c r="AP122" s="12"/>
     </row>
-    <row r="123" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A123" s="70">
         <v>46188</v>
       </c>
@@ -19408,7 +19407,7 @@
       </c>
       <c r="AP123" s="12"/>
     </row>
-    <row r="124" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A124" s="70">
         <v>46188</v>
       </c>
@@ -19542,7 +19541,7 @@
       </c>
       <c r="AP124" s="12"/>
     </row>
-    <row r="125" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A125" s="70">
         <v>46188</v>
       </c>
@@ -19676,7 +19675,7 @@
       </c>
       <c r="AP125" s="12"/>
     </row>
-    <row r="126" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A126" s="70">
         <v>46188</v>
       </c>
@@ -19810,7 +19809,7 @@
       </c>
       <c r="AP126" s="12"/>
     </row>
-    <row r="127" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A127" s="70">
         <v>46188</v>
       </c>
@@ -19944,7 +19943,7 @@
       </c>
       <c r="AP127" s="12"/>
     </row>
-    <row r="128" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A128" s="70">
         <v>46188</v>
       </c>
@@ -20078,7 +20077,7 @@
       </c>
       <c r="AP128" s="12"/>
     </row>
-    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A129" s="70">
         <v>46188</v>
       </c>
@@ -20212,7 +20211,7 @@
       </c>
       <c r="AP129" s="12"/>
     </row>
-    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A130" s="70">
         <v>46188</v>
       </c>
@@ -20344,7 +20343,7 @@
       </c>
       <c r="AP130" s="12"/>
     </row>
-    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A131" s="70">
         <v>46188</v>
       </c>
@@ -21274,7 +21273,7 @@
       </c>
       <c r="AP137" s="12"/>
     </row>
-    <row r="138" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A138" s="70">
         <v>46189</v>
       </c>
@@ -21408,7 +21407,7 @@
       </c>
       <c r="AP138" s="12"/>
     </row>
-    <row r="139" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A139" s="70">
         <v>46189</v>
       </c>
@@ -21542,7 +21541,7 @@
       </c>
       <c r="AP139" s="12"/>
     </row>
-    <row r="140" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A140" s="70">
         <v>46189</v>
       </c>
@@ -21676,7 +21675,7 @@
       </c>
       <c r="AP140" s="12"/>
     </row>
-    <row r="141" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A141" s="70">
         <v>46189</v>
       </c>
@@ -21810,7 +21809,7 @@
       </c>
       <c r="AP141" s="12"/>
     </row>
-    <row r="142" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A142" s="70">
         <v>46189</v>
       </c>
@@ -21944,7 +21943,7 @@
       </c>
       <c r="AP142" s="12"/>
     </row>
-    <row r="143" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A143" s="70">
         <v>46189</v>
       </c>
@@ -22078,7 +22077,7 @@
       </c>
       <c r="AP143" s="12"/>
     </row>
-    <row r="144" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A144" s="70">
         <v>46189</v>
       </c>
@@ -22212,7 +22211,7 @@
       </c>
       <c r="AP144" s="12"/>
     </row>
-    <row r="145" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A145" s="70">
         <v>46189</v>
       </c>
@@ -22346,7 +22345,7 @@
       </c>
       <c r="AP145" s="12"/>
     </row>
-    <row r="146" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A146" s="70">
         <v>46189</v>
       </c>
@@ -22480,7 +22479,7 @@
       </c>
       <c r="AP146" s="12"/>
     </row>
-    <row r="147" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A147" s="70">
         <v>46189</v>
       </c>
@@ -22614,7 +22613,7 @@
       </c>
       <c r="AP147" s="12"/>
     </row>
-    <row r="148" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A148" s="70">
         <v>46189</v>
       </c>
@@ -22748,7 +22747,7 @@
       </c>
       <c r="AP148" s="12"/>
     </row>
-    <row r="149" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A149" s="70">
         <v>46189</v>
       </c>
@@ -22882,7 +22881,7 @@
       </c>
       <c r="AP149" s="12"/>
     </row>
-    <row r="150" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A150" s="70">
         <v>46189</v>
       </c>
@@ -23016,7 +23015,7 @@
       </c>
       <c r="AP150" s="12"/>
     </row>
-    <row r="151" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A151" s="70">
         <v>46189</v>
       </c>
@@ -23150,7 +23149,7 @@
       </c>
       <c r="AP151" s="12"/>
     </row>
-    <row r="152" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A152" s="70">
         <v>46190</v>
       </c>
@@ -23284,7 +23283,7 @@
       </c>
       <c r="AP152" s="12"/>
     </row>
-    <row r="153" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A153" s="70">
         <v>46190</v>
       </c>
@@ -23418,7 +23417,7 @@
       </c>
       <c r="AP153" s="12"/>
     </row>
-    <row r="154" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A154" s="70">
         <v>46190</v>
       </c>
@@ -23550,7 +23549,7 @@
       </c>
       <c r="AP154" s="12"/>
     </row>
-    <row r="155" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A155" s="70">
         <v>46190</v>
       </c>
@@ -23682,7 +23681,7 @@
       </c>
       <c r="AP155" s="12"/>
     </row>
-    <row r="156" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A156" s="70">
         <v>46190</v>
       </c>
@@ -23814,7 +23813,7 @@
       </c>
       <c r="AP156" s="12"/>
     </row>
-    <row r="157" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A157" s="70">
         <v>46190</v>
       </c>
@@ -23948,7 +23947,7 @@
       </c>
       <c r="AP157" s="12"/>
     </row>
-    <row r="158" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A158" s="70">
         <v>46190</v>
       </c>
@@ -24082,7 +24081,7 @@
       </c>
       <c r="AP158" s="12"/>
     </row>
-    <row r="159" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A159" s="70">
         <v>46190</v>
       </c>
@@ -24216,7 +24215,7 @@
       </c>
       <c r="AP159" s="12"/>
     </row>
-    <row r="160" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A160" s="70">
         <v>46190</v>
       </c>
@@ -26462,7 +26461,7 @@
       </c>
       <c r="AP176" s="12"/>
     </row>
-    <row r="177" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A177" s="70">
         <v>46191</v>
       </c>
@@ -26596,7 +26595,7 @@
       </c>
       <c r="AP177" s="12"/>
     </row>
-    <row r="178" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A178" s="70">
         <v>46191</v>
       </c>
@@ -26730,7 +26729,7 @@
       </c>
       <c r="AP178" s="12"/>
     </row>
-    <row r="179" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A179" s="70">
         <v>46191</v>
       </c>
@@ -26864,7 +26863,7 @@
       </c>
       <c r="AP179" s="12"/>
     </row>
-    <row r="180" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A180" s="70">
         <v>46191</v>
       </c>
@@ -26998,7 +26997,7 @@
       </c>
       <c r="AP180" s="12"/>
     </row>
-    <row r="181" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A181" s="70">
         <v>46191</v>
       </c>
@@ -27132,7 +27131,7 @@
       </c>
       <c r="AP181" s="12"/>
     </row>
-    <row r="182" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A182" s="70">
         <v>46191</v>
       </c>
@@ -27266,7 +27265,7 @@
       </c>
       <c r="AP182" s="12"/>
     </row>
-    <row r="183" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A183" s="70">
         <v>46191</v>
       </c>
@@ -27400,7 +27399,7 @@
       </c>
       <c r="AP183" s="12"/>
     </row>
-    <row r="184" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A184" s="70">
         <v>46191</v>
       </c>
@@ -27534,7 +27533,7 @@
       </c>
       <c r="AP184" s="12"/>
     </row>
-    <row r="185" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A185" s="70">
         <v>46191</v>
       </c>
@@ -27668,7 +27667,7 @@
       </c>
       <c r="AP185" s="12"/>
     </row>
-    <row r="186" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A186" s="70">
         <v>46191</v>
       </c>
@@ -30442,7 +30441,7 @@
       </c>
       <c r="AP206" s="12"/>
     </row>
-    <row r="207" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A207" s="70">
         <v>46192</v>
       </c>
@@ -30574,7 +30573,7 @@
       </c>
       <c r="AP207" s="12"/>
     </row>
-    <row r="208" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A208" s="70">
         <v>46192</v>
       </c>
@@ -30706,7 +30705,7 @@
       </c>
       <c r="AP208" s="12"/>
     </row>
-    <row r="209" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A209" s="70">
         <v>46192</v>
       </c>
@@ -30840,7 +30839,7 @@
       </c>
       <c r="AP209" s="12"/>
     </row>
-    <row r="210" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A210" s="70">
         <v>46192</v>
       </c>
@@ -30972,7 +30971,7 @@
       </c>
       <c r="AP210" s="12"/>
     </row>
-    <row r="211" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A211" s="70">
         <v>46192</v>
       </c>
@@ -31104,7 +31103,7 @@
       </c>
       <c r="AP211" s="12"/>
     </row>
-    <row r="212" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A212" s="70">
         <v>46192</v>
       </c>
@@ -31236,7 +31235,7 @@
       </c>
       <c r="AP212" s="12"/>
     </row>
-    <row r="213" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A213" s="70">
         <v>46192</v>
       </c>
@@ -33348,7 +33347,7 @@
       </c>
       <c r="AP228" s="12"/>
     </row>
-    <row r="229" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A229" s="70">
         <v>46193</v>
       </c>
@@ -33482,7 +33481,7 @@
       </c>
       <c r="AP229" s="12"/>
     </row>
-    <row r="230" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A230" s="70">
         <v>46193</v>
       </c>
@@ -33616,7 +33615,7 @@
       </c>
       <c r="AP230" s="12"/>
     </row>
-    <row r="231" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A231" s="70">
         <v>46193</v>
       </c>
@@ -33750,7 +33749,7 @@
       </c>
       <c r="AP231" s="12"/>
     </row>
-    <row r="232" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A232" s="70">
         <v>46193</v>
       </c>
@@ -33884,7 +33883,7 @@
       </c>
       <c r="AP232" s="12"/>
     </row>
-    <row r="233" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A233" s="70">
         <v>46193</v>
       </c>
@@ -34018,7 +34017,7 @@
       </c>
       <c r="AP233" s="12"/>
     </row>
-    <row r="234" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A234" s="70">
         <v>46193</v>
       </c>
@@ -34152,7 +34151,7 @@
       </c>
       <c r="AP234" s="12"/>
     </row>
-    <row r="235" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A235" s="70">
         <v>46193</v>
       </c>
@@ -34286,7 +34285,7 @@
       </c>
       <c r="AP235" s="12"/>
     </row>
-    <row r="236" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A236" s="70">
         <v>46193</v>
       </c>
@@ -34420,7 +34419,7 @@
       </c>
       <c r="AP236" s="12"/>
     </row>
-    <row r="237" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A237" s="70">
         <v>46193</v>
       </c>
@@ -34554,7 +34553,7 @@
       </c>
       <c r="AP237" s="12"/>
     </row>
-    <row r="238" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A238" s="70">
         <v>46193</v>
       </c>
@@ -34688,7 +34687,7 @@
       </c>
       <c r="AP238" s="12"/>
     </row>
-    <row r="239" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A239" s="70">
         <v>46193</v>
       </c>
@@ -34822,7 +34821,7 @@
       </c>
       <c r="AP239" s="12"/>
     </row>
-    <row r="240" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A240" s="70">
         <v>46193</v>
       </c>
@@ -34956,7 +34955,7 @@
       </c>
       <c r="AP240" s="12"/>
     </row>
-    <row r="241" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A241" s="70">
         <v>46193</v>
       </c>
@@ -35090,7 +35089,7 @@
       </c>
       <c r="AP241" s="12"/>
     </row>
-    <row r="242" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A242" s="70">
         <v>46193</v>
       </c>
@@ -35224,7 +35223,7 @@
       </c>
       <c r="AP242" s="12"/>
     </row>
-    <row r="243" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A243" s="70">
         <v>46193</v>
       </c>
@@ -35358,7 +35357,7 @@
       </c>
       <c r="AP243" s="12"/>
     </row>
-    <row r="244" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A244" s="70">
         <v>46193</v>
       </c>
@@ -35492,7 +35491,7 @@
       </c>
       <c r="AP244" s="12"/>
     </row>
-    <row r="245" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A245" s="70">
         <v>46193</v>
       </c>
@@ -35626,7 +35625,7 @@
       </c>
       <c r="AP245" s="12"/>
     </row>
-    <row r="246" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A246" s="70">
         <v>46193</v>
       </c>
@@ -35760,7 +35759,7 @@
       </c>
       <c r="AP246" s="12"/>
     </row>
-    <row r="247" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A247" s="70">
         <v>46193</v>
       </c>
@@ -35894,7 +35893,7 @@
       </c>
       <c r="AP247" s="12"/>
     </row>
-    <row r="248" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A248" s="70">
         <v>46193</v>
       </c>
@@ -36028,7 +36027,7 @@
       </c>
       <c r="AP248" s="12"/>
     </row>
-    <row r="249" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A249" s="70">
         <v>46193</v>
       </c>
@@ -36428,7 +36427,7 @@
       </c>
       <c r="AP251" s="12"/>
     </row>
-    <row r="252" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A252" s="70">
         <v>46195</v>
       </c>
@@ -36556,7 +36555,7 @@
       </c>
       <c r="AP252" s="12"/>
     </row>
-    <row r="253" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A253" s="70">
         <v>46195</v>
       </c>
@@ -36814,7 +36813,7 @@
       </c>
       <c r="AP254" s="12"/>
     </row>
-    <row r="255" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A255" s="70">
         <v>46195</v>
       </c>
@@ -36938,7 +36937,7 @@
       </c>
       <c r="AP255" s="12"/>
     </row>
-    <row r="256" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A256" s="70">
         <v>46195</v>
       </c>
@@ -37070,7 +37069,7 @@
       </c>
       <c r="AP256" s="12"/>
     </row>
-    <row r="257" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A257" s="70">
         <v>46195</v>
       </c>
@@ -37196,7 +37195,7 @@
       </c>
       <c r="AP257" s="12"/>
     </row>
-    <row r="258" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A258" s="70">
         <v>46195</v>
       </c>
@@ -37322,7 +37321,7 @@
       </c>
       <c r="AP258" s="12"/>
     </row>
-    <row r="259" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A259" s="70">
         <v>46195</v>
       </c>
@@ -37454,7 +37453,7 @@
       </c>
       <c r="AP259" s="12"/>
     </row>
-    <row r="260" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A260" s="70">
         <v>46195</v>
       </c>
@@ -37578,7 +37577,7 @@
       </c>
       <c r="AP260" s="12"/>
     </row>
-    <row r="261" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A261" s="70">
         <v>46195</v>
       </c>
@@ -37700,7 +37699,7 @@
       </c>
       <c r="AP261" s="12"/>
     </row>
-    <row r="262" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A262" s="70">
         <v>46195</v>
       </c>
@@ -37826,7 +37825,7 @@
       </c>
       <c r="AP262" s="12"/>
     </row>
-    <row r="263" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A263" s="70">
         <v>46195</v>
       </c>
@@ -37954,7 +37953,7 @@
       </c>
       <c r="AP263" s="12"/>
     </row>
-    <row r="264" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A264" s="70">
         <v>46195</v>
       </c>
@@ -38082,7 +38081,7 @@
       </c>
       <c r="AP264" s="12"/>
     </row>
-    <row r="265" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A265" s="70">
         <v>46195</v>
       </c>
@@ -38208,7 +38207,7 @@
       </c>
       <c r="AP265" s="12"/>
     </row>
-    <row r="266" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A266" s="70">
         <v>46195</v>
       </c>
@@ -38330,7 +38329,7 @@
       </c>
       <c r="AP266" s="12"/>
     </row>
-    <row r="267" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A267" s="70">
         <v>46195</v>
       </c>
@@ -38462,7 +38461,7 @@
       </c>
       <c r="AP267" s="12"/>
     </row>
-    <row r="268" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A268" s="70">
         <v>46195</v>
       </c>
@@ -38588,7 +38587,7 @@
       </c>
       <c r="AP268" s="12"/>
     </row>
-    <row r="269" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A269" s="70">
         <v>46195</v>
       </c>
@@ -38716,7 +38715,7 @@
       </c>
       <c r="AP269" s="12"/>
     </row>
-    <row r="270" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A270" s="70">
         <v>46195</v>
       </c>
@@ -38842,7 +38841,7 @@
       </c>
       <c r="AP270" s="12"/>
     </row>
-    <row r="271" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A271" s="70">
         <v>46195</v>
       </c>
@@ -38974,7 +38973,7 @@
       </c>
       <c r="AP271" s="12"/>
     </row>
-    <row r="272" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A272" s="70">
         <v>46195</v>
       </c>
@@ -39102,7 +39101,7 @@
       </c>
       <c r="AP272" s="12"/>
     </row>
-    <row r="273" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A273" s="70">
         <v>46195</v>
       </c>
@@ -39228,7 +39227,7 @@
       </c>
       <c r="AP273" s="12"/>
     </row>
-    <row r="274" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A274" s="70">
         <v>46195</v>
       </c>
@@ -39352,7 +39351,7 @@
       </c>
       <c r="AP274" s="12"/>
     </row>
-    <row r="275" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A275" s="70">
         <v>46195</v>
       </c>
@@ -39476,7 +39475,7 @@
       </c>
       <c r="AP275" s="12"/>
     </row>
-    <row r="276" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A276" s="70">
         <v>46195</v>
       </c>
@@ -39602,7 +39601,7 @@
       </c>
       <c r="AP276" s="12"/>
     </row>
-    <row r="277" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A277" s="70">
         <v>46195</v>
       </c>
@@ -39724,7 +39723,7 @@
       </c>
       <c r="AP277" s="12"/>
     </row>
-    <row r="278" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A278" s="70">
         <v>46195</v>
       </c>
@@ -39846,7 +39845,7 @@
       </c>
       <c r="AP278" s="12"/>
     </row>
-    <row r="279" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A279" s="70">
         <v>46195</v>
       </c>
@@ -39968,7 +39967,7 @@
       </c>
       <c r="AP279" s="12"/>
     </row>
-    <row r="280" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A280" s="70">
         <v>46195</v>
       </c>
@@ -40102,7 +40101,7 @@
       </c>
       <c r="AP280" s="12"/>
     </row>
-    <row r="281" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A281" s="70">
         <v>46196</v>
       </c>
@@ -40224,7 +40223,7 @@
       </c>
       <c r="AP281" s="12"/>
     </row>
-    <row r="282" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A282" s="70">
         <v>46196</v>
       </c>
@@ -40350,7 +40349,7 @@
       </c>
       <c r="AP282" s="12"/>
     </row>
-    <row r="283" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A283" s="70">
         <v>46196</v>
       </c>
@@ -40482,7 +40481,7 @@
       </c>
       <c r="AP283" s="12"/>
     </row>
-    <row r="284" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A284" s="70">
         <v>46196</v>
       </c>
@@ -40610,7 +40609,7 @@
       </c>
       <c r="AP284" s="12"/>
     </row>
-    <row r="285" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A285" s="70">
         <v>46196</v>
       </c>
@@ -40738,7 +40737,7 @@
       </c>
       <c r="AP285" s="12"/>
     </row>
-    <row r="286" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A286" s="70">
         <v>46196</v>
       </c>
@@ -40866,7 +40865,7 @@
       </c>
       <c r="AP286" s="12"/>
     </row>
-    <row r="287" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A287" s="70">
         <v>46196</v>
       </c>
@@ -41000,7 +40999,7 @@
       </c>
       <c r="AP287" s="12"/>
     </row>
-    <row r="288" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A288" s="70">
         <v>46196</v>
       </c>
@@ -41124,7 +41123,7 @@
       </c>
       <c r="AP288" s="12"/>
     </row>
-    <row r="289" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A289" s="70">
         <v>46196</v>
       </c>
@@ -41246,7 +41245,7 @@
       </c>
       <c r="AP289" s="12"/>
     </row>
-    <row r="290" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A290" s="70">
         <v>46196</v>
       </c>
@@ -41368,7 +41367,7 @@
       </c>
       <c r="AP290" s="12"/>
     </row>
-    <row r="291" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A291" s="70">
         <v>46196</v>
       </c>
@@ -41490,7 +41489,7 @@
       </c>
       <c r="AP291" s="12"/>
     </row>
-    <row r="292" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A292" s="70">
         <v>46196</v>
       </c>
@@ -41618,7 +41617,7 @@
       </c>
       <c r="AP292" s="12"/>
     </row>
-    <row r="293" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A293" s="70">
         <v>46196</v>
       </c>
@@ -41744,7 +41743,7 @@
       </c>
       <c r="AP293" s="12"/>
     </row>
-    <row r="294" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A294" s="70">
         <v>46196</v>
       </c>
@@ -41876,7 +41875,7 @@
       </c>
       <c r="AP294" s="12"/>
     </row>
-    <row r="295" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A295" s="70">
         <v>46196</v>
       </c>
@@ -42008,7 +42007,7 @@
       </c>
       <c r="AP295" s="12"/>
     </row>
-    <row r="296" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A296" s="70">
         <v>46196</v>
       </c>
@@ -42134,7 +42133,7 @@
       </c>
       <c r="AP296" s="12"/>
     </row>
-    <row r="297" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A297" s="70">
         <v>46196</v>
       </c>
@@ -42266,7 +42265,7 @@
       </c>
       <c r="AP297" s="12"/>
     </row>
-    <row r="298" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A298" s="70">
         <v>46196</v>
       </c>
@@ -42388,7 +42387,7 @@
       </c>
       <c r="AP298" s="12"/>
     </row>
-    <row r="299" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A299" s="70">
         <v>46196</v>
       </c>
@@ -42510,7 +42509,7 @@
       </c>
       <c r="AP299" s="12"/>
     </row>
-    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A300" s="70">
         <v>46197</v>
       </c>
@@ -42634,7 +42633,7 @@
       </c>
       <c r="AP300" s="12"/>
     </row>
-    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A301" s="70">
         <v>46197</v>
       </c>
@@ -42762,7 +42761,7 @@
       </c>
       <c r="AP301" s="12"/>
     </row>
-    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A302" s="70">
         <v>46197</v>
       </c>
@@ -42890,7 +42889,7 @@
       </c>
       <c r="AP302" s="12"/>
     </row>
-    <row r="303" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A303" s="70">
         <v>46197</v>
       </c>
@@ -43016,7 +43015,7 @@
       </c>
       <c r="AP303" s="12"/>
     </row>
-    <row r="304" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A304" s="70">
         <v>46197</v>
       </c>
@@ -43142,7 +43141,7 @@
       </c>
       <c r="AP304" s="12"/>
     </row>
-    <row r="305" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A305" s="70">
         <v>46197</v>
       </c>
@@ -43264,7 +43263,7 @@
       </c>
       <c r="AP305" s="12"/>
     </row>
-    <row r="306" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A306" s="70">
         <v>46197</v>
       </c>
@@ -43396,7 +43395,7 @@
       </c>
       <c r="AP306" s="12"/>
     </row>
-    <row r="307" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A307" s="70">
         <v>46197</v>
       </c>
@@ -43520,7 +43519,7 @@
       </c>
       <c r="AP307" s="12"/>
     </row>
-    <row r="308" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A308" s="70">
         <v>46197</v>
       </c>
@@ -43654,7 +43653,7 @@
       </c>
       <c r="AP308" s="12"/>
     </row>
-    <row r="309" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A309" s="70">
         <v>46197</v>
       </c>
@@ -43784,7 +43783,7 @@
       </c>
       <c r="AP309" s="12"/>
     </row>
-    <row r="310" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A310" s="70">
         <v>46197</v>
       </c>
@@ -43914,7 +43913,7 @@
       </c>
       <c r="AP310" s="12"/>
     </row>
-    <row r="311" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A311" s="70">
         <v>46197</v>
       </c>
@@ -44036,7 +44035,7 @@
       </c>
       <c r="AP311" s="12"/>
     </row>
-    <row r="312" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A312" s="70">
         <v>46197</v>
       </c>
@@ -44158,7 +44157,7 @@
       </c>
       <c r="AP312" s="12"/>
     </row>
-    <row r="313" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A313" s="70">
         <v>46197</v>
       </c>
@@ -44280,7 +44279,7 @@
       </c>
       <c r="AP313" s="12"/>
     </row>
-    <row r="314" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A314" s="70">
         <v>46197</v>
       </c>
@@ -44408,7 +44407,7 @@
       </c>
       <c r="AP314" s="12"/>
     </row>
-    <row r="315" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A315" s="70">
         <v>46197</v>
       </c>
@@ -44534,7 +44533,7 @@
       </c>
       <c r="AP315" s="12"/>
     </row>
-    <row r="316" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A316" s="70">
         <v>46197</v>
       </c>
@@ -44656,7 +44655,7 @@
       </c>
       <c r="AP316" s="12"/>
     </row>
-    <row r="317" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A317" s="70">
         <v>46197</v>
       </c>
@@ -44778,7 +44777,7 @@
       </c>
       <c r="AP317" s="12"/>
     </row>
-    <row r="318" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A318" s="70">
         <v>46197</v>
       </c>
@@ -47108,7 +47107,7 @@
       </c>
       <c r="AP335" s="12"/>
     </row>
-    <row r="336" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A336" s="70">
         <v>46202</v>
       </c>
@@ -47236,7 +47235,7 @@
       </c>
       <c r="AP336" s="12"/>
     </row>
-    <row r="337" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A337" s="70">
         <v>46202</v>
       </c>
@@ -47360,7 +47359,7 @@
       </c>
       <c r="AP337" s="12"/>
     </row>
-    <row r="338" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A338" s="70">
         <v>46202</v>
       </c>
@@ -47486,7 +47485,7 @@
       </c>
       <c r="AP338" s="12"/>
     </row>
-    <row r="339" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A339" s="70">
         <v>46202</v>
       </c>
@@ -47610,7 +47609,7 @@
       </c>
       <c r="AP339" s="12"/>
     </row>
-    <row r="340" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A340" s="70">
         <v>46202</v>
       </c>
@@ -47744,7 +47743,7 @@
       </c>
       <c r="AP340" s="12"/>
     </row>
-    <row r="341" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A341" s="70">
         <v>46202</v>
       </c>
@@ -47874,7 +47873,7 @@
       </c>
       <c r="AP341" s="12"/>
     </row>
-    <row r="342" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A342" s="70">
         <v>46202</v>
       </c>
@@ -48004,7 +48003,7 @@
       </c>
       <c r="AP342" s="12"/>
     </row>
-    <row r="343" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A343" s="70">
         <v>46202</v>
       </c>
@@ -48132,7 +48131,7 @@
       </c>
       <c r="AP343" s="12"/>
     </row>
-    <row r="344" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A344" s="70">
         <v>46202</v>
       </c>
@@ -48262,7 +48261,7 @@
       </c>
       <c r="AP344" s="12"/>
     </row>
-    <row r="345" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A345" s="70">
         <v>46202</v>
       </c>
@@ -48392,7 +48391,7 @@
       </c>
       <c r="AP345" s="12"/>
     </row>
-    <row r="346" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A346" s="70">
         <v>46202</v>
       </c>
@@ -48522,7 +48521,7 @@
       </c>
       <c r="AP346" s="12"/>
     </row>
-    <row r="347" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A347" s="70">
         <v>46202</v>
       </c>
@@ -48650,7 +48649,7 @@
       </c>
       <c r="AP347" s="12"/>
     </row>
-    <row r="348" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A348" s="70">
         <v>46202</v>
       </c>
@@ -48774,7 +48773,7 @@
       </c>
       <c r="AP348" s="12"/>
     </row>
-    <row r="349" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A349" s="70">
         <v>46202</v>
       </c>
@@ -50850,7 +50849,7 @@
       </c>
       <c r="AP364" s="12"/>
     </row>
-    <row r="365" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A365" s="70">
         <v>46203</v>
       </c>
@@ -50976,7 +50975,7 @@
       </c>
       <c r="AP365" s="12"/>
     </row>
-    <row r="366" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A366" s="70">
         <v>46203</v>
       </c>
@@ -51098,7 +51097,7 @@
       </c>
       <c r="AP366" s="12"/>
     </row>
-    <row r="367" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A367" s="70">
         <v>46203</v>
       </c>
@@ -51226,7 +51225,7 @@
       </c>
       <c r="AP367" s="12"/>
     </row>
-    <row r="368" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A368" s="70">
         <v>46203</v>
       </c>
@@ -51352,7 +51351,7 @@
       </c>
       <c r="AP368" s="12"/>
     </row>
-    <row r="369" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A369" s="70">
         <v>46203</v>
       </c>
@@ -51476,7 +51475,7 @@
       </c>
       <c r="AP369" s="12"/>
     </row>
-    <row r="370" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A370" s="70">
         <v>46203</v>
       </c>
@@ -51598,7 +51597,7 @@
       </c>
       <c r="AP370" s="12"/>
     </row>
-    <row r="371" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A371" s="70">
         <v>46203</v>
       </c>
@@ -51728,7 +51727,7 @@
       </c>
       <c r="AP371" s="12"/>
     </row>
-    <row r="372" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A372" s="70">
         <v>46203</v>
       </c>
@@ -51852,7 +51851,7 @@
       </c>
       <c r="AP372" s="12"/>
     </row>
-    <row r="373" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A373" s="70">
         <v>46203</v>
       </c>
@@ -51976,7 +51975,7 @@
       </c>
       <c r="AP373" s="12"/>
     </row>
-    <row r="374" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A374" s="70">
         <v>46203</v>
       </c>
@@ -52104,7 +52103,7 @@
       </c>
       <c r="AP374" s="12"/>
     </row>
-    <row r="375" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A375" s="70">
         <v>46203</v>
       </c>
@@ -52228,7 +52227,7 @@
       </c>
       <c r="AP375" s="12"/>
     </row>
-    <row r="376" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A376" s="70">
         <v>46203</v>
       </c>
@@ -52352,7 +52351,7 @@
       </c>
       <c r="AP376" s="12"/>
     </row>
-    <row r="377" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A377" s="70">
         <v>46203</v>
       </c>
@@ -52476,7 +52475,7 @@
       </c>
       <c r="AP377" s="12"/>
     </row>
-    <row r="378" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A378" s="70">
         <v>46203</v>
       </c>
@@ -52606,7 +52605,7 @@
       </c>
       <c r="AP378" s="12"/>
     </row>
-    <row r="379" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A379" s="70">
         <v>46203</v>
       </c>
@@ -52738,7 +52737,7 @@
       </c>
       <c r="AP379" s="12"/>
     </row>
-    <row r="380" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A380" s="70">
         <v>46203</v>
       </c>
@@ -52866,7 +52865,7 @@
       </c>
       <c r="AP380" s="12"/>
     </row>
-    <row r="381" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A381" s="70">
         <v>46203</v>
       </c>
@@ -52992,7 +52991,7 @@
       </c>
       <c r="AP381" s="12"/>
     </row>
-    <row r="382" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A382" s="70">
         <v>46203</v>
       </c>
@@ -53120,7 +53119,7 @@
       </c>
       <c r="AP382" s="12"/>
     </row>
-    <row r="383" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A383" s="70">
         <v>46203</v>
       </c>
@@ -53252,7 +53251,7 @@
       </c>
       <c r="AP383" s="12"/>
     </row>
-    <row r="384" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A384" s="70">
         <v>46203</v>
       </c>
@@ -53384,7 +53383,7 @@
       </c>
       <c r="AP384" s="12"/>
     </row>
-    <row r="385" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A385" s="70">
         <v>46203</v>
       </c>
@@ -53512,7 +53511,7 @@
       </c>
       <c r="AP385" s="12"/>
     </row>
-    <row r="386" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A386" s="70">
         <v>46203</v>
       </c>
@@ -53634,7 +53633,7 @@
       </c>
       <c r="AP386" s="12"/>
     </row>
-    <row r="387" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A387" s="70">
         <v>46203</v>
       </c>
@@ -53760,7 +53759,7 @@
       </c>
       <c r="AP387" s="12"/>
     </row>
-    <row r="388" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A388" s="70">
         <v>46203</v>
       </c>
@@ -53884,7 +53883,7 @@
       </c>
       <c r="AP388" s="12"/>
     </row>
-    <row r="389" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A389" s="70">
         <v>46203</v>
       </c>
@@ -54006,7 +54005,7 @@
       </c>
       <c r="AP389" s="12"/>
     </row>
-    <row r="390" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A390" s="70">
         <v>46203</v>
       </c>
@@ -54128,7 +54127,7 @@
       </c>
       <c r="AP390" s="12"/>
     </row>
-    <row r="391" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A391" s="70">
         <v>46203</v>
       </c>
@@ -54250,7 +54249,7 @@
       </c>
       <c r="AP391" s="12"/>
     </row>
-    <row r="392" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A392" s="70">
         <v>46203</v>
       </c>
@@ -54372,7 +54371,7 @@
       </c>
       <c r="AP392" s="12"/>
     </row>
-    <row r="393" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A393" s="70">
         <v>46203</v>
       </c>
@@ -54494,7 +54493,7 @@
       </c>
       <c r="AP393" s="12"/>
     </row>
-    <row r="394" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A394" s="70">
         <v>46203</v>
       </c>
@@ -56046,7 +56045,7 @@
       </c>
       <c r="AP405" s="12"/>
     </row>
-    <row r="406" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A406" s="17"/>
       <c r="C406" s="18"/>
       <c r="E406" s="6"/>
@@ -56143,7 +56142,7 @@
       </c>
       <c r="AP406" s="12"/>
     </row>
-    <row r="407" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A407" s="17"/>
       <c r="C407" s="18"/>
       <c r="E407" s="6"/>
@@ -56240,7 +56239,7 @@
       </c>
       <c r="AP407" s="12"/>
     </row>
-    <row r="408" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A408" s="17"/>
       <c r="C408" s="18"/>
       <c r="E408" s="6"/>
@@ -56337,7 +56336,7 @@
       </c>
       <c r="AP408" s="12"/>
     </row>
-    <row r="409" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A409" s="17"/>
       <c r="C409" s="18"/>
       <c r="E409" s="6"/>
@@ -56434,7 +56433,7 @@
       </c>
       <c r="AP409" s="12"/>
     </row>
-    <row r="410" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A410" s="17"/>
       <c r="C410" s="18"/>
       <c r="E410" s="6"/>
@@ -56531,7 +56530,7 @@
       </c>
       <c r="AP410" s="12"/>
     </row>
-    <row r="411" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A411" s="17"/>
       <c r="C411" s="18"/>
       <c r="E411" s="6"/>
@@ -56628,7 +56627,7 @@
       </c>
       <c r="AP411" s="12"/>
     </row>
-    <row r="412" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A412" s="17"/>
       <c r="C412" s="18"/>
       <c r="E412" s="6"/>
@@ -56725,7 +56724,7 @@
       </c>
       <c r="AP412" s="12"/>
     </row>
-    <row r="413" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A413" s="17"/>
       <c r="C413" s="18"/>
       <c r="E413" s="6"/>
@@ -56822,7 +56821,7 @@
       </c>
       <c r="AP413" s="12"/>
     </row>
-    <row r="414" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A414" s="17"/>
       <c r="C414" s="18"/>
       <c r="E414" s="6"/>
@@ -56919,7 +56918,7 @@
       </c>
       <c r="AP414" s="12"/>
     </row>
-    <row r="415" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A415" s="17"/>
       <c r="C415" s="18"/>
       <c r="E415" s="6"/>
@@ -57016,7 +57015,7 @@
       </c>
       <c r="AP415" s="12"/>
     </row>
-    <row r="416" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A416" s="17"/>
       <c r="C416" s="18"/>
       <c r="E416" s="6"/>
@@ -57113,7 +57112,7 @@
       </c>
       <c r="AP416" s="12"/>
     </row>
-    <row r="417" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A417" s="17"/>
       <c r="C417" s="18"/>
       <c r="E417" s="6"/>
@@ -57210,7 +57209,7 @@
       </c>
       <c r="AP417" s="12"/>
     </row>
-    <row r="418" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A418" s="17"/>
       <c r="C418" s="18"/>
       <c r="E418" s="6"/>
@@ -57307,7 +57306,7 @@
       </c>
       <c r="AP418" s="12"/>
     </row>
-    <row r="419" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A419" s="17"/>
       <c r="C419" s="18"/>
       <c r="E419" s="6"/>
@@ -57404,7 +57403,7 @@
       </c>
       <c r="AP419" s="12"/>
     </row>
-    <row r="420" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A420" s="17"/>
       <c r="C420" s="18"/>
       <c r="E420" s="6"/>
@@ -57501,7 +57500,7 @@
       </c>
       <c r="AP420" s="12"/>
     </row>
-    <row r="421" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A421" s="17"/>
       <c r="C421" s="18"/>
       <c r="E421" s="6"/>
@@ -57598,7 +57597,7 @@
       </c>
       <c r="AP421" s="12"/>
     </row>
-    <row r="422" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A422" s="17"/>
       <c r="C422" s="18"/>
       <c r="E422" s="6"/>
@@ -57695,7 +57694,7 @@
       </c>
       <c r="AP422" s="12"/>
     </row>
-    <row r="423" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A423" s="17"/>
       <c r="C423" s="18"/>
       <c r="E423" s="6"/>
@@ -57792,7 +57791,7 @@
       </c>
       <c r="AP423" s="12"/>
     </row>
-    <row r="424" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A424" s="17"/>
       <c r="C424" s="18"/>
       <c r="E424" s="6"/>
@@ -57889,7 +57888,7 @@
       </c>
       <c r="AP424" s="12"/>
     </row>
-    <row r="425" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A425" s="6"/>
       <c r="C425" s="6"/>
       <c r="E425" s="6"/>
@@ -58202,34 +58201,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP425" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="Shakoor"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="10" showButton="0"/>
-    <filterColumn colId="11" showButton="0"/>
-    <filterColumn colId="12" showButton="0"/>
-    <filterColumn colId="14" showButton="0"/>
-    <filterColumn colId="15" showButton="0"/>
-    <filterColumn colId="16" showButton="0"/>
-    <filterColumn colId="19" showButton="0"/>
-    <filterColumn colId="20" showButton="0"/>
-    <filterColumn colId="21" showButton="0"/>
-    <filterColumn colId="23" showButton="0"/>
-    <filterColumn colId="24" showButton="0"/>
-    <filterColumn colId="25" showButton="0"/>
-  </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58242,13 +58221,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
